--- a/output/pdf_financials_xlsx/TMG.xlsx
+++ b/output/pdf_financials_xlsx/TMG.xlsx
@@ -2145,49 +2145,49 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.103246</v>
+        <v>0.153268</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.09912600000000001</v>
+        <v>0.144977</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.09829499999999999</v>
+        <v>0.143918</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.008303</v>
+        <v>0.046704</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.036077</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.038344</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.038114</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.044342</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.253976</v>
+        <v>0.338485</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.28058</v>
+        <v>0.5169010000000001</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.270867</v>
+        <v>0.559413</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.305904</v>
+        <v>0.697016</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.230536</v>
+        <v>0.6129250000000001</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0.225389</v>
+        <v>0.723032</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.154464</v>
+        <v>0.759724</v>
       </c>
     </row>
     <row r="29">
@@ -2207,49 +2207,49 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.006015</v>
+        <v>0.044007</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.222408</v>
+        <v>0.268259</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.942577</v>
+        <v>-2.896954</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.716722</v>
+        <v>0.755123</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.318271</v>
+        <v>-2.282194</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.356474</v>
+        <v>0.394818</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.5925</v>
+        <v>0.630614</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.521004</v>
+        <v>0.565346</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.30583</v>
+        <v>-0.221321</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.919988</v>
+        <v>-1.683667</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.289682</v>
+        <v>0.578228</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.443511</v>
+        <v>-1.052399</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.924471</v>
+        <v>1.30686</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>1.224538</v>
+        <v>1.722181</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>0.33458</v>
+        <v>0.93984</v>
       </c>
     </row>
     <row r="30">
@@ -2269,49 +2269,49 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-0.0620064993944702</v>
+        <v>0.4536525384625851</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1.690970065660348</v>
+        <v>2.039575639563231</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-35.84035485468502</v>
+        <v>-35.28467032730127</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>5.450021709689365</v>
+        <v>5.742026536768457</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-34.0912580115385</v>
+        <v>-33.56072887353768</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2.874309107604243</v>
+        <v>3.183483152336754</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>4.491321970023439</v>
+        <v>4.780237152412424</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>2.992863540084619</v>
+        <v>3.247582419583495</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-1.450582395812108</v>
+        <v>-1.049747723975841</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-8.965130327894686</v>
+        <v>-7.861660637345371</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>1.887262020495232</v>
+        <v>3.767123064556711</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-9.073438918401523</v>
+        <v>-6.615036563134499</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>4.383130321735177</v>
+        <v>6.196124802468474</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>4.731563673955032</v>
+        <v>6.654435435711714</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>1.123487750833801</v>
+        <v>3.155893142876561</v>
       </c>
     </row>
     <row r="31">
@@ -6371,55 +6371,55 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.170958</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.1865</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.153268</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.144977</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.143918</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.046704</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.036077</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.038344</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.038114</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.044342</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.338485</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.5169010000000001</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.559413</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.697016</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.6129250000000001</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.723032</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.759724</v>
       </c>
     </row>
     <row r="101">
@@ -7088,16 +7088,16 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.008076</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.009157</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.006833</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
@@ -7106,10 +7106,10 @@
         <v>0</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.001245</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.001933</v>
       </c>
       <c r="Q112" s="3" t="n">
         <v>0</v>
@@ -30508,7 +30508,11 @@
           <t>Depreciation of property, plant and equipment (note 9)</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -30605,7 +30609,11 @@
           <t>Depreciation of right-of-use assets (note 10)</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -30803,7 +30811,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -33940,7 +33948,11 @@
           <t>Proceeds from disposal of property, plant and equipment (note 9)</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -34621,7 +34633,11 @@
           <t>Depreciation of property, plant and equipment (note 8)</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -34716,7 +34732,11 @@
           <t>Depreciation of right-of-use assets (note 9)</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -34912,7 +34932,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -35597,7 +35617,11 @@
           <t>Proceeds from disposal of property, plant and equipment (note 8)</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -35795,7 +35819,11 @@
           <t>Additions to intangible assets (note 10)</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -37757,7 +37785,11 @@
           <t>Depreciation of property, plant and equipment (note 10)</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -37854,7 +37886,11 @@
           <t>Depreciation of right-of-use assets (note 13)</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -38945,7 +38981,11 @@
           <t>Proceeds from disposal of property, plant and equipment (note 10)</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -40848,7 +40888,11 @@
           <t>Depreciation of property, plant and equipment (note 9)</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
@@ -41788,7 +41832,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -42974,7 +43022,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -43980,7 +44028,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -44079,7 +44131,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E364" s="5" t="n">

--- a/output/pdf_financials_xlsx/TMG.xlsx
+++ b/output/pdf_financials_xlsx/TMG.xlsx
@@ -1402,19 +1402,19 @@
         <v>0.199768</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.09847499999999999</v>
+        <v>-0.09847499999999999</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.108703</v>
+        <v>-0.108703</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.303611</v>
+        <v>-0.303611</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.20415</v>
+        <v>-0.20415</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0.088556</v>
+        <v>0.088556</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>-0.026514</v>
@@ -3793,13 +3793,11 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0.597472</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>0.582535</v>
       </c>
       <c r="D56" s="3" t="n">
         <v>0</v>
@@ -3853,13 +3851,11 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0.44851</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>0.486851</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>0</v>
@@ -4657,22 +4653,22 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.105269</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.215923</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.193298</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.214684</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.308996</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.39451</v>
       </c>
     </row>
     <row r="71">
@@ -4717,22 +4713,22 @@
         <v>0.371993</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0.269886</v>
+        <v>0.375155</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0.850987</v>
+        <v>1.06691</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0.79644</v>
+        <v>0.989738</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0.919057</v>
+        <v>1.133741</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0.921018</v>
+        <v>1.230014</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0.327757</v>
+        <v>0.722267</v>
       </c>
     </row>
     <row r="72">
@@ -4953,22 +4949,22 @@
         <v>2.065464</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>3.9849</v>
+        <v>3.879631</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>2.354907</v>
+        <v>2.138984</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>2.377205</v>
+        <v>2.183907</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>4.985979</v>
+        <v>4.771295</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>5.437073</v>
+        <v>5.128077</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>4.469556</v>
+        <v>4.075046</v>
       </c>
     </row>
     <row r="76">
@@ -5133,22 +5129,22 @@
         <v>0</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0</v>
+        <v>0.431976</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0</v>
+        <v>1.337141</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>0</v>
+        <v>1.177582</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>0</v>
+        <v>1.248295</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>0</v>
+        <v>1.234971</v>
       </c>
       <c r="R78" s="3" t="n">
-        <v>0</v>
+        <v>0.864393</v>
       </c>
     </row>
     <row r="79">
@@ -5193,22 +5189,22 @@
         <v>2.633867</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>2.489786</v>
+        <v>2.921762</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>2.409439</v>
+        <v>3.74658</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>3.139914</v>
+        <v>4.317496</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>2.34626</v>
+        <v>3.594555</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>1.429733</v>
+        <v>2.664704</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>0.00164</v>
+        <v>0.8660330000000001</v>
       </c>
     </row>
     <row r="80">
@@ -5271,22 +5267,22 @@
         <v>0.7718114946212041</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>1.375475741898183</v>
+        <v>1.64324939940389</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>1.100409730941099</v>
+        <v>1.624576431358255</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>3.772148599322876</v>
+        <v>5.085842203058654</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>1.698041591479935</v>
+        <v>2.458825058892662</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.6868718773749773</v>
+        <v>1.138007498244653</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>0.09234696309171701</v>
+        <v>0.4452823841096735</v>
       </c>
     </row>
     <row r="81">
@@ -5571,22 +5567,22 @@
         <v>0.110148</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>0.431976</v>
+        <v>0</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>1.337141</v>
+        <v>0</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>1.177582</v>
+        <v>0</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>1.248295</v>
+        <v>0</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>1.234971</v>
+        <v>0</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>0.864393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -10229,7 +10225,11 @@
           <t>Current portion of lease obligations (note 17)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -10506,7 +10506,11 @@
           <t>Lease obligations (note 17)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -12279,7 +12283,11 @@
           <t>Current portion of lease obligations (note 16)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -12481,7 +12489,11 @@
           <t>Lease obligations (note 16)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -13843,7 +13855,11 @@
           <t>Current portion of lease obligations (note 15)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -14037,7 +14053,11 @@
           <t>Lease obligations (note 15)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -15631,7 +15651,11 @@
           <t>Lease obligations (note 18)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -15936,7 +15960,11 @@
           <t>Lease obligations (note 18)</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -44226,7 +44254,11 @@
           <t>Deferred income taxes (recovery)</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -46131,7 +46163,11 @@
           <t>Deferred income taxes (recovery) (Note 23)</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -47034,7 +47070,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -54654,7 +54694,11 @@
           <t>Income taxes recovery (expense) (note 23)</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E471" t="inlineStr">
         <is>
           <t>-</t>
@@ -55828,7 +55872,11 @@
           <t>Income taxes recovery (note 23)</t>
         </is>
       </c>
-      <c r="D483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E483" t="inlineStr">
         <is>
           <t>-</t>
@@ -56828,7 +56876,11 @@
           <t>Income taxes recovery (note 26)</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
           <t>-</t>
@@ -58632,7 +58684,11 @@
           <t>Income tax recovery (expense) (note 24)</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E511" t="inlineStr">
         <is>
           <t>-</t>
